--- a/Excel Practice @ Day 01.xlsx
+++ b/Excel Practice @ Day 01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codegnan\Data Analytics\Microsoft Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d89171c96d88985/Desktop/EXCEL1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EDD6B2-0724-4318-9899-D620E8A3924E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{E520F339-BDD3-4986-9E54-910913B99090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67CCCC65-474B-444A-B7F9-502866BAA23E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FB56502-8CCC-4FEF-933B-4B92691D64CD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5FB56502-8CCC-4FEF-933B-4B92691D64CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="144">
   <si>
     <t>Product</t>
   </si>
@@ -449,6 +449,27 @@
   </si>
   <si>
     <t>A18*D17</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>k6*k4</t>
+  </si>
+  <si>
+    <t>k7*k4</t>
+  </si>
+  <si>
+    <t>l6*l4</t>
+  </si>
+  <si>
+    <t>l7*l4</t>
+  </si>
+  <si>
+    <t>m6*m4</t>
+  </si>
+  <si>
+    <t>m7*m4</t>
   </si>
 </sst>
 </file>
@@ -460,7 +481,7 @@
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,9 +728,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -747,7 +768,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -853,7 +874,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -995,7 +1016,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1004,12 +1025,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434D2FB2-2A93-4150-8783-1D0D51BE71F1}">
   <dimension ref="A2:N25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+    <col min="12" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="43.2">
+    <row r="2" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
@@ -1036,13 +1059,19 @@
       <c r="C3" s="14">
         <v>2</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="14">
+        <f>B3*C3</f>
+        <v>80000</v>
+      </c>
+      <c r="E3" s="15">
+        <f>D3/$D$6</f>
+        <v>0.83333333333333337</v>
+      </c>
       <c r="K3" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
@@ -1052,8 +1081,14 @@
       <c r="C4" s="14">
         <v>5</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
+      <c r="D4" s="14">
+        <f t="shared" ref="D4:D5" si="0">B4*C4</f>
+        <v>10000</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:E5" si="1">D4/$D$6</f>
+        <v>0.10416666666666667</v>
+      </c>
       <c r="J4" s="12"/>
       <c r="K4" s="16">
         <v>0.4</v>
@@ -1065,7 +1100,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
@@ -1075,8 +1110,14 @@
       <c r="C5" s="14">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="E5" s="15">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
       <c r="J5" s="12" t="s">
         <v>2</v>
       </c>
@@ -1090,7 +1131,14 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v>96000</v>
+      </c>
       <c r="J6" t="s">
         <v>125</v>
       </c>
@@ -1104,7 +1152,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="J7" t="s">
         <v>126</v>
       </c>
@@ -1118,7 +1166,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="27" customHeight="1">
+    <row r="8" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>4</v>
       </c>
@@ -1154,7 +1202,10 @@
       <c r="C9" s="17">
         <v>0.1</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="14">
+        <f>B9*C9</f>
+        <v>5000</v>
+      </c>
       <c r="J9" t="s">
         <v>128</v>
       </c>
@@ -1168,15 +1219,20 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="14">
         <v>1000</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="14">
+        <f t="shared" ref="D10:D11" si="2">B10*C10</f>
+        <v>100</v>
+      </c>
       <c r="J10" t="s">
         <v>129</v>
       </c>
@@ -1190,15 +1246,20 @@
         <v>246</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="14">
         <v>2000</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="14"/>
+      <c r="C11" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="14">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
       <c r="J11" t="s">
         <v>130</v>
       </c>
@@ -1212,15 +1273,15 @@
         <v>390</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="J14" s="12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K15" t="s">
         <v>122</v>
       </c>
@@ -1234,7 +1295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1243,12 +1304,24 @@
       <c r="J16" t="s">
         <v>125</v>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="13"/>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="K16" s="16">
+        <f>K6*K$4</f>
+        <v>145.6</v>
+      </c>
+      <c r="L16" s="16">
+        <f>L6*L$4</f>
+        <v>469.2</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" ref="M16:N16" si="3">M6*M$4</f>
+        <v>26.4</v>
+      </c>
+      <c r="N16" s="16">
+        <f>SUM(K16:M16)</f>
+        <v>641.19999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>1</v>
       </c>
@@ -1267,12 +1340,24 @@
       <c r="J17" t="s">
         <v>126</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="K17" s="16">
+        <f t="shared" ref="K17:M21" si="4">K7*K$4</f>
+        <v>154.80000000000001</v>
+      </c>
+      <c r="L17" s="16">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" si="4"/>
+        <v>37.68</v>
+      </c>
+      <c r="N17" s="16">
+        <f t="shared" ref="N17:N22" si="5">SUM(K17:M17)</f>
+        <v>486.48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="19">
         <v>1</v>
       </c>
@@ -1281,158 +1366,218 @@
         <v>1</v>
       </c>
       <c r="C18" s="18">
-        <f t="shared" ref="C18:F22" si="0">$A18*C$17</f>
+        <f t="shared" ref="C18:F22" si="6">$A18*C$17</f>
         <v>2</v>
       </c>
       <c r="D18" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="E18" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="F18" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="J18" t="s">
         <v>127</v>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="13"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="K18" s="16">
+        <f t="shared" si="4"/>
+        <v>116</v>
+      </c>
+      <c r="L18" s="16">
+        <f t="shared" si="4"/>
+        <v>253.2</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="N18" s="16">
+        <f t="shared" si="5"/>
+        <v>393.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="19">
         <v>2</v>
       </c>
       <c r="B19" s="18">
-        <f t="shared" ref="B19:B22" si="1">$A19*B$17</f>
+        <f t="shared" ref="B19:B22" si="7">$A19*B$17</f>
         <v>2</v>
       </c>
       <c r="C19" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D19" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="E19" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="F19" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="J19" t="s">
         <v>128</v>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="13"/>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="K19" s="16">
+        <f t="shared" si="4"/>
+        <v>136</v>
+      </c>
+      <c r="L19" s="16">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="4"/>
+        <v>39.6</v>
+      </c>
+      <c r="N19" s="16">
+        <f t="shared" si="5"/>
+        <v>493.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="19">
         <v>3</v>
       </c>
       <c r="B20" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="C20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="D20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="E20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="F20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="J20" t="s">
         <v>129</v>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="13"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="K20" s="16">
+        <f t="shared" si="4"/>
+        <v>104.4</v>
+      </c>
+      <c r="L20" s="16">
+        <f t="shared" si="4"/>
+        <v>414</v>
+      </c>
+      <c r="M20" s="16">
+        <f t="shared" si="4"/>
+        <v>29.52</v>
+      </c>
+      <c r="N20" s="16">
+        <f t="shared" si="5"/>
+        <v>547.91999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="19">
         <v>4</v>
       </c>
       <c r="B21" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="C21" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="D21" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="E21" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="J21" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="13"/>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="K21" s="16">
+        <f t="shared" si="4"/>
+        <v>146</v>
+      </c>
+      <c r="L21" s="16">
+        <f t="shared" si="4"/>
+        <v>278.39999999999998</v>
+      </c>
+      <c r="M21" s="16">
+        <f t="shared" si="4"/>
+        <v>46.8</v>
+      </c>
+      <c r="N21" s="16">
+        <f t="shared" si="5"/>
+        <v>471.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="19">
         <v>5</v>
       </c>
       <c r="B22" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="C22" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="D22" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="E22" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="13"/>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="K22" s="16">
+        <f>SUM(K16:K21)</f>
+        <v>802.8</v>
+      </c>
+      <c r="L22" s="16">
+        <f>SUM(L16:L21)</f>
+        <v>2026.8000000000002</v>
+      </c>
+      <c r="M22" s="16">
+        <f>SUM(M16:M21)</f>
+        <v>204</v>
+      </c>
+      <c r="N22" s="13">
+        <f>SUM(N16:N21)</f>
+        <v>3033.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>132</v>
       </c>
@@ -1442,13 +1587,31 @@
       <c r="D23" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="K23" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="K24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L24" t="s">
+        <v>141</v>
+      </c>
+      <c r="M24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>134</v>
       </c>
@@ -1461,24 +1624,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E67C3A7-D518-4B6A-A9BB-C5AD5EC3E129}">
   <dimension ref="A1:P39"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="48.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" customWidth="1"/>
+    <col min="12" max="12" width="48.6328125" customWidth="1"/>
+    <col min="13" max="13" width="13.08984375" customWidth="1"/>
+    <col min="14" max="14" width="11.6328125" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
@@ -1507,7 +1670,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>150834</v>
       </c>
@@ -1536,7 +1699,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>150784</v>
       </c>
@@ -1565,7 +1728,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>150791</v>
       </c>
@@ -1598,7 +1761,7 @@
       </c>
       <c r="M4" s="21"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>150940</v>
       </c>
@@ -1631,7 +1794,7 @@
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>150777</v>
       </c>
@@ -1664,7 +1827,7 @@
       </c>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>150805</v>
       </c>
@@ -1697,7 +1860,7 @@
       </c>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>150990</v>
       </c>
@@ -1730,7 +1893,7 @@
       </c>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>150989</v>
       </c>
@@ -1763,7 +1926,7 @@
       </c>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>150881</v>
       </c>
@@ -1796,7 +1959,7 @@
       </c>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>150814</v>
       </c>
@@ -1825,7 +1988,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>150937</v>
       </c>
@@ -1858,7 +2021,7 @@
       </c>
       <c r="M12" s="21"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>150888</v>
       </c>
@@ -1891,7 +2054,7 @@
       </c>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>150865</v>
       </c>
@@ -1924,7 +2087,7 @@
       </c>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>150858</v>
       </c>
@@ -1957,7 +2120,7 @@
       </c>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>150930</v>
       </c>
@@ -1990,7 +2153,7 @@
       </c>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>150894</v>
       </c>
@@ -2023,7 +2186,7 @@
       </c>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>150947</v>
       </c>
@@ -2056,7 +2219,7 @@
       </c>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>150905</v>
       </c>
@@ -2085,7 +2248,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>150995</v>
       </c>
@@ -2114,7 +2277,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>150912</v>
       </c>
@@ -2143,7 +2306,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>150921</v>
       </c>
@@ -2176,7 +2339,7 @@
       </c>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>150851</v>
       </c>
@@ -2220,7 +2383,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>150867</v>
       </c>
@@ -2256,7 +2419,7 @@
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>150899</v>
       </c>
@@ -2292,7 +2455,7 @@
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>150975</v>
       </c>
@@ -2328,7 +2491,7 @@
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>150901</v>
       </c>
@@ -2364,7 +2527,7 @@
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>150968</v>
       </c>
@@ -2400,7 +2563,7 @@
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>150773</v>
       </c>
@@ -2436,7 +2599,7 @@
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>150840</v>
       </c>
@@ -2472,7 +2635,7 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>150850</v>
       </c>
@@ -2508,7 +2671,7 @@
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>150962</v>
       </c>
@@ -2544,7 +2707,7 @@
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>150954</v>
       </c>
@@ -2580,7 +2743,7 @@
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>150874</v>
       </c>
@@ -2616,7 +2779,7 @@
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>150798</v>
       </c>
@@ -2645,7 +2808,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>150830</v>
       </c>
@@ -2674,7 +2837,7 @@
         <v>52000</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>150929</v>
       </c>
@@ -2703,7 +2866,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>150982</v>
       </c>
@@ -2732,7 +2895,7 @@
         <v>47000</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>150821</v>
       </c>
